--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_INSOLAC CB ALCALÁ CAJA87.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_INSOLAC CB ALCALÁ CAJA87.xlsx
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>H. ANDRADE CORREIA E SILVA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>6.284600000000001</v>
+        <v>3.1016</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1345</v>
+        <v>19.0143</v>
       </c>
       <c r="F4" t="n">
-        <v>5.149800000000001</v>
+        <v>-15.9126</v>
       </c>
       <c r="G4" t="n">
-        <v>-9.716200000000001</v>
+        <v>27.4846</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.8193</v>
+        <v>8.5876</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.8964</v>
+        <v>18.8969</v>
       </c>
       <c r="J4" t="n">
-        <v>10.6692</v>
+        <v>68.7578</v>
       </c>
       <c r="K4" t="n">
-        <v>5.308800000000001</v>
+        <v>32.1327</v>
       </c>
       <c r="L4" t="n">
-        <v>5.3607</v>
+        <v>36.6253</v>
       </c>
       <c r="M4" t="n">
-        <v>-20.3856</v>
+        <v>-41.2733</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.1285</v>
+        <v>-23.5449</v>
       </c>
       <c r="O4" t="n">
-        <v>-10.2572</v>
+        <v>-17.7284</v>
       </c>
       <c r="P4" t="n">
-        <v>3.335399999999999</v>
+        <v>-17.0463</v>
       </c>
       <c r="Q4" t="n">
-        <v>-32.0548</v>
+        <v>-68.0004</v>
       </c>
       <c r="R4" t="n">
-        <v>35.3898</v>
+        <v>50.954</v>
       </c>
       <c r="S4" t="n">
-        <v>11.2155</v>
+        <v>-4.944</v>
       </c>
       <c r="T4" t="n">
-        <v>5.5304</v>
+        <v>-2.1939</v>
       </c>
       <c r="U4" t="n">
-        <v>5.685</v>
+        <v>-2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.450499999999999</v>
+        <v>-2.3926</v>
       </c>
       <c r="W4" t="n">
-        <v>16.9897</v>
+        <v>20.4505</v>
       </c>
       <c r="X4" t="n">
-        <v>-15.5393</v>
+        <v>-22.8431</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>3.969399999999999</v>
+        <v>1.163</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5065</v>
+        <v>-1.092</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5370000000000004</v>
+        <v>2.2547</v>
       </c>
       <c r="G5" t="n">
-        <v>-22.8555</v>
+        <v>-9.716200000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.499700000000001</v>
+        <v>-4.8193</v>
       </c>
       <c r="I5" t="n">
-        <v>-19.3559</v>
+        <v>-4.8964</v>
       </c>
       <c r="J5" t="n">
-        <v>18.2195</v>
+        <v>10.6692</v>
       </c>
       <c r="K5" t="n">
-        <v>17.6193</v>
+        <v>5.308800000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6001000000000001</v>
+        <v>5.3607</v>
       </c>
       <c r="M5" t="n">
-        <v>-41.0749</v>
+        <v>-20.3856</v>
       </c>
       <c r="N5" t="n">
-        <v>-21.1191</v>
+        <v>-10.1285</v>
       </c>
       <c r="O5" t="n">
-        <v>-19.9557</v>
+        <v>-10.2572</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.7794</v>
+        <v>3.335399999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-53.7333</v>
+        <v>-32.0548</v>
       </c>
       <c r="R5" t="n">
-        <v>50.954</v>
+        <v>35.3898</v>
       </c>
       <c r="S5" t="n">
-        <v>21.7343</v>
+        <v>6.0939</v>
       </c>
       <c r="T5" t="n">
-        <v>18.9385</v>
+        <v>3.3036</v>
       </c>
       <c r="U5" t="n">
-        <v>2.796</v>
+        <v>2.79</v>
       </c>
       <c r="V5" t="n">
-        <v>7.870199999999999</v>
+        <v>1.450499999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>21.0823</v>
+        <v>16.9897</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.2122</v>
+        <v>-15.5393</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.197</v>
+        <v>-0.0974</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4431</v>
+        <v>-0.639</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2461</v>
+        <v>0.5416</v>
       </c>
       <c r="G6" t="n">
         <v>0.3049</v>
@@ -922,13 +922,13 @@
         <v>0.1853</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4245</v>
+        <v>0.5241</v>
       </c>
       <c r="T6" t="n">
-        <v>0.434</v>
+        <v>0.2381</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0095</v>
+        <v>0.286</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>C. VALDES ALVAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2766999999999995</v>
+        <v>-1.0191</v>
       </c>
       <c r="E7" t="n">
-        <v>8.8931</v>
+        <v>0.8212000000000002</v>
       </c>
       <c r="F7" t="n">
-        <v>-9.1698</v>
+        <v>-1.8401</v>
       </c>
       <c r="G7" t="n">
-        <v>-12.8113</v>
+        <v>-2.0607</v>
       </c>
       <c r="H7" t="n">
-        <v>-9.077999999999999</v>
+        <v>-0.7352999999999998</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.7334</v>
+        <v>-1.3254</v>
       </c>
       <c r="J7" t="n">
-        <v>2.704400000000001</v>
+        <v>-0.5677000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.287599999999999</v>
+        <v>-0.1637999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9919</v>
+        <v>-0.4041</v>
       </c>
       <c r="M7" t="n">
-        <v>-15.5158</v>
+        <v>-1.493</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.7906</v>
+        <v>-0.5715</v>
       </c>
       <c r="O7" t="n">
-        <v>-7.7252</v>
+        <v>-0.9215</v>
       </c>
       <c r="P7" t="n">
-        <v>7.4114</v>
+        <v>1.1117</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.188</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>12.5994</v>
+        <v>2.0382</v>
       </c>
       <c r="S7" t="n">
-        <v>8.899100000000001</v>
+        <v>-0.0706</v>
       </c>
       <c r="T7" t="n">
-        <v>7.601900000000001</v>
+        <v>-0.2024</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2971</v>
+        <v>0.1318</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.7761</v>
+        <v>0.0006000000000000449</v>
       </c>
       <c r="W7" t="n">
-        <v>3.775</v>
+        <v>2.5177</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.5509</v>
+        <v>-2.5171</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. VALDES ALVAREZ</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5668999999999995</v>
+        <v>-4.344800000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2561</v>
+        <v>-4.604099999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.823</v>
+        <v>0.2588999999999995</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0607</v>
+        <v>-22.8555</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7352999999999998</v>
+        <v>-3.499700000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3254</v>
+        <v>-19.3559</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5677000000000001</v>
+        <v>18.2195</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1637999999999999</v>
+        <v>17.6193</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4041</v>
+        <v>0.6001000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.493</v>
+        <v>-41.0749</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5715</v>
+        <v>-21.1191</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9215</v>
+        <v>-19.9557</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1117</v>
+        <v>-2.7794</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>-53.7333</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0382</v>
+        <v>50.954</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3815</v>
+        <v>13.4197</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2326</v>
+        <v>9.8278</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1489</v>
+        <v>3.592</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0006000000000000449</v>
+        <v>7.870199999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5177</v>
+        <v>21.0823</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.5171</v>
+        <v>-13.2122</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ AMESTOY</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.812</v>
+        <v>-5.208</v>
       </c>
       <c r="E9" t="n">
-        <v>7.072100000000001</v>
+        <v>4.7916</v>
       </c>
       <c r="F9" t="n">
-        <v>-13.8842</v>
+        <v>-9.999600000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.6409</v>
+        <v>-12.8113</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.1281</v>
+        <v>-9.077999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5127999999999999</v>
+        <v>-3.7334</v>
       </c>
       <c r="J9" t="n">
-        <v>7.4182</v>
+        <v>2.704400000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0587</v>
+        <v>-1.287599999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>5.3597</v>
+        <v>3.9919</v>
       </c>
       <c r="M9" t="n">
-        <v>-16.0592</v>
+        <v>-15.5158</v>
       </c>
       <c r="N9" t="n">
-        <v>-10.1868</v>
+        <v>-7.7906</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.8726</v>
+        <v>-7.7252</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.782</v>
+        <v>7.4114</v>
       </c>
       <c r="Q9" t="n">
-        <v>-28.1632</v>
+        <v>-5.188</v>
       </c>
       <c r="R9" t="n">
-        <v>20.3814</v>
+        <v>12.5994</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5197999999999997</v>
+        <v>3.9679</v>
       </c>
       <c r="T9" t="n">
-        <v>4.2209</v>
+        <v>3.5004</v>
       </c>
       <c r="U9" t="n">
-        <v>-4.7407</v>
+        <v>0.4676</v>
       </c>
       <c r="V9" t="n">
-        <v>10.1307</v>
+        <v>-3.7761</v>
       </c>
       <c r="W9" t="n">
-        <v>23.5967</v>
+        <v>3.775</v>
       </c>
       <c r="X9" t="n">
-        <v>-13.4661</v>
+        <v>-7.5509</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ORLANDO ROMERO</t>
+          <t>A. FERNANDEZ AMESTOY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.9355</v>
+        <v>-5.8099</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3284</v>
+        <v>6.0527</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.607</v>
+        <v>-11.8624</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0815</v>
+        <v>-8.6409</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5976</v>
+        <v>-8.1281</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4839</v>
+        <v>-0.5127999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.0525</v>
+        <v>7.4182</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1769</v>
+        <v>2.0587</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8757</v>
+        <v>5.3597</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.02900000000000003</v>
+        <v>-16.0592</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4207</v>
+        <v>-10.1868</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3917</v>
+        <v>-5.8726</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9264</v>
+        <v>-7.782</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1117</v>
+        <v>-28.1632</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1853</v>
+        <v>20.3814</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2196</v>
+        <v>0.4825</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1641</v>
+        <v>3.201</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3837</v>
+        <v>-2.7184</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.1472</v>
+        <v>10.1307</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>23.5967</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.1472</v>
+        <v>-13.4661</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.5837</v>
+        <v>-6.167899999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-14.8686</v>
+        <v>-2.266000000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>5.284699999999999</v>
+        <v>-3.9019</v>
       </c>
       <c r="G11" t="n">
-        <v>-15.555</v>
+        <v>-7.692500000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.436000000000001</v>
+        <v>-10.5427</v>
       </c>
       <c r="I11" t="n">
-        <v>-13.1191</v>
+        <v>2.8504</v>
       </c>
       <c r="J11" t="n">
-        <v>24.3349</v>
+        <v>25.8719</v>
       </c>
       <c r="K11" t="n">
-        <v>21.2453</v>
+        <v>9.3087</v>
       </c>
       <c r="L11" t="n">
-        <v>3.0896</v>
+        <v>16.5633</v>
       </c>
       <c r="M11" t="n">
-        <v>-39.8897</v>
+        <v>-33.5641</v>
       </c>
       <c r="N11" t="n">
-        <v>-23.6815</v>
+        <v>-19.8514</v>
       </c>
       <c r="O11" t="n">
-        <v>-16.2086</v>
+        <v>-13.7128</v>
       </c>
       <c r="P11" t="n">
-        <v>1.482099999999999</v>
+        <v>3.334999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-49.101</v>
+        <v>-36.3161</v>
       </c>
       <c r="R11" t="n">
-        <v>50.5831</v>
+        <v>39.6511</v>
       </c>
       <c r="S11" t="n">
-        <v>4.5512</v>
+        <v>-1.6878</v>
       </c>
       <c r="T11" t="n">
-        <v>2.663</v>
+        <v>-2.5203</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8885</v>
+        <v>0.8326</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.06229999999999969</v>
+        <v>-0.1233999999999993</v>
       </c>
       <c r="W11" t="n">
-        <v>7.2348</v>
+        <v>10.6986</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.2974</v>
+        <v>-10.822</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. ANDRADE CORREIA E SILVA</t>
+          <t>A. ORLANDO ROMERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.9075</v>
+        <v>-6.691</v>
       </c>
       <c r="E12" t="n">
-        <v>10.1201</v>
+        <v>-4.0346</v>
       </c>
       <c r="F12" t="n">
-        <v>-21.0271</v>
+        <v>-2.6563</v>
       </c>
       <c r="G12" t="n">
-        <v>27.4846</v>
+        <v>-3.0815</v>
       </c>
       <c r="H12" t="n">
-        <v>8.5876</v>
+        <v>-1.5976</v>
       </c>
       <c r="I12" t="n">
-        <v>18.8969</v>
+        <v>-1.4839</v>
       </c>
       <c r="J12" t="n">
-        <v>68.7578</v>
+        <v>-3.0525</v>
       </c>
       <c r="K12" t="n">
-        <v>32.1327</v>
+        <v>-1.1769</v>
       </c>
       <c r="L12" t="n">
-        <v>36.6253</v>
+        <v>-1.8757</v>
       </c>
       <c r="M12" t="n">
-        <v>-41.2733</v>
+        <v>-0.02900000000000003</v>
       </c>
       <c r="N12" t="n">
-        <v>-23.5449</v>
+        <v>-0.4207</v>
       </c>
       <c r="O12" t="n">
-        <v>-17.7284</v>
+        <v>0.3917</v>
       </c>
       <c r="P12" t="n">
-        <v>-17.0463</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q12" t="n">
-        <v>-68.0004</v>
+        <v>-1.1117</v>
       </c>
       <c r="R12" t="n">
-        <v>50.954</v>
+        <v>0.1853</v>
       </c>
       <c r="S12" t="n">
-        <v>-18.9527</v>
+        <v>0.4641</v>
       </c>
       <c r="T12" t="n">
-        <v>-11.0882</v>
+        <v>0.1296</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.8647</v>
+        <v>0.3345</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3926</v>
+        <v>-3.1472</v>
       </c>
       <c r="W12" t="n">
-        <v>20.4505</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-22.8431</v>
+        <v>-3.1472</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.2144</v>
+        <v>-9.243399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.907700000000002</v>
+        <v>-14.5807</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3065</v>
+        <v>5.3371</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.692500000000001</v>
+        <v>-15.555</v>
       </c>
       <c r="H13" t="n">
-        <v>-10.5427</v>
+        <v>-2.436000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8504</v>
+        <v>-13.1191</v>
       </c>
       <c r="J13" t="n">
-        <v>25.8719</v>
+        <v>24.3349</v>
       </c>
       <c r="K13" t="n">
-        <v>9.3087</v>
+        <v>21.2453</v>
       </c>
       <c r="L13" t="n">
-        <v>16.5633</v>
+        <v>3.0896</v>
       </c>
       <c r="M13" t="n">
-        <v>-33.5641</v>
+        <v>-39.8897</v>
       </c>
       <c r="N13" t="n">
-        <v>-19.8514</v>
+        <v>-23.6815</v>
       </c>
       <c r="O13" t="n">
-        <v>-13.7128</v>
+        <v>-16.2086</v>
       </c>
       <c r="P13" t="n">
-        <v>3.334999999999999</v>
+        <v>1.482099999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-36.3161</v>
+        <v>-49.101</v>
       </c>
       <c r="R13" t="n">
-        <v>39.6511</v>
+        <v>50.5831</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.734</v>
+        <v>4.8914</v>
       </c>
       <c r="T13" t="n">
-        <v>-9.162100000000001</v>
+        <v>2.9507</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4278</v>
+        <v>1.9408</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1233999999999993</v>
+        <v>-0.06229999999999969</v>
       </c>
       <c r="W13" t="n">
-        <v>10.6986</v>
+        <v>7.2348</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.822</v>
+        <v>-7.2974</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.2456</v>
+        <v>-11.5001</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.7425</v>
+        <v>-12.8589</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4971</v>
+        <v>1.359</v>
       </c>
       <c r="G14" t="n">
         <v>-13.31</v>
@@ -1546,13 +1546,13 @@
         <v>7.2263</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0904</v>
+        <v>0.6551</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8904</v>
+        <v>0.9935</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2</v>
+        <v>-0.3384</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0686</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ALVAREZ RICO</t>
+          <t>A. VICENTE FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.8304</v>
+        <v>-14.5531</v>
       </c>
       <c r="E15" t="n">
-        <v>-21.5549</v>
+        <v>-12.8114</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7245</v>
+        <v>-1.7418</v>
       </c>
       <c r="G15" t="n">
-        <v>-23.1986</v>
+        <v>-14.3071</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.193</v>
+        <v>-14.1496</v>
       </c>
       <c r="I15" t="n">
-        <v>-17.0054</v>
+        <v>-0.1577000000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8197</v>
+        <v>5.9563</v>
       </c>
       <c r="K15" t="n">
-        <v>9.7674</v>
+        <v>-0.1502000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>-6.9476</v>
+        <v>6.1066</v>
       </c>
       <c r="M15" t="n">
-        <v>-26.0181</v>
+        <v>-20.2637</v>
       </c>
       <c r="N15" t="n">
-        <v>-15.9605</v>
+        <v>-13.999</v>
       </c>
       <c r="O15" t="n">
-        <v>-10.0575</v>
+        <v>-6.2647</v>
       </c>
       <c r="P15" t="n">
-        <v>-8.152799999999999</v>
+        <v>0.1852000000000005</v>
       </c>
       <c r="Q15" t="n">
-        <v>-41.5042</v>
+        <v>-35.3899</v>
       </c>
       <c r="R15" t="n">
-        <v>33.3515</v>
+        <v>35.5751</v>
       </c>
       <c r="S15" t="n">
-        <v>10.5564</v>
+        <v>-1.1237</v>
       </c>
       <c r="T15" t="n">
-        <v>6.12</v>
+        <v>1.8336</v>
       </c>
       <c r="U15" t="n">
-        <v>4.4368</v>
+        <v>-2.9574</v>
       </c>
       <c r="V15" t="n">
-        <v>3.9643</v>
+        <v>0.6923000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>11.0099</v>
+        <v>14.7886</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.045500000000001</v>
+        <v>-14.0963</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>-17.0248</v>
+        <v>-14.9797</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.0109</v>
+        <v>-8.898999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.014099999999999</v>
+        <v>-6.0805</v>
       </c>
       <c r="G16" t="n">
         <v>-14.6534</v>
@@ -1702,13 +1702,13 @@
         <v>7.4116</v>
       </c>
       <c r="S16" t="n">
-        <v>0.03420000000000017</v>
+        <v>2.0792</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4964</v>
+        <v>1.6079</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4623</v>
+        <v>0.4713000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-3.1465</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VICENTE FERNANDEZ</t>
+          <t>A. GONZALEZ PALOMO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>-19.7532</v>
+        <v>-17.5459</v>
       </c>
       <c r="E17" t="n">
-        <v>-16.1666</v>
+        <v>-6.4333</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.5862</v>
+        <v>-11.1122</v>
       </c>
       <c r="G17" t="n">
-        <v>-14.3071</v>
+        <v>-5.6047</v>
       </c>
       <c r="H17" t="n">
-        <v>-14.1496</v>
+        <v>2.5128</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1577000000000002</v>
+        <v>-8.117599999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>5.9563</v>
+        <v>8.3569</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1502000000000001</v>
+        <v>7.4827</v>
       </c>
       <c r="L17" t="n">
-        <v>6.1066</v>
+        <v>0.8739999999999994</v>
       </c>
       <c r="M17" t="n">
-        <v>-20.2637</v>
+        <v>-13.9615</v>
       </c>
       <c r="N17" t="n">
-        <v>-13.999</v>
+        <v>-4.970000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-6.2647</v>
+        <v>-8.9916</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1852000000000005</v>
+        <v>-5.9292</v>
       </c>
       <c r="Q17" t="n">
-        <v>-35.3899</v>
+        <v>-21.4933</v>
       </c>
       <c r="R17" t="n">
-        <v>35.5751</v>
+        <v>15.564</v>
       </c>
       <c r="S17" t="n">
-        <v>-6.3234</v>
+        <v>-0.8508</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.5217</v>
+        <v>-0.8482</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.8018</v>
+        <v>-0.002700000000000008</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6923000000000001</v>
+        <v>-5.1608</v>
       </c>
       <c r="W17" t="n">
-        <v>14.7886</v>
+        <v>7.5515</v>
       </c>
       <c r="X17" t="n">
-        <v>-14.0963</v>
+        <v>-12.7123</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>A. ALVAREZ RICO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-22.8135</v>
+        <v>-18.2282</v>
       </c>
       <c r="E18" t="n">
-        <v>-11.7086</v>
+        <v>-22.3988</v>
       </c>
       <c r="F18" t="n">
-        <v>-11.105</v>
+        <v>4.1712</v>
       </c>
       <c r="G18" t="n">
-        <v>-20.6761</v>
+        <v>-23.1986</v>
       </c>
       <c r="H18" t="n">
-        <v>-16.4596</v>
+        <v>-6.193</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.2166</v>
+        <v>-17.0054</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.8446</v>
+        <v>2.8197</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.208499999999999</v>
+        <v>9.7674</v>
       </c>
       <c r="L18" t="n">
-        <v>2.3639</v>
+        <v>-6.9476</v>
       </c>
       <c r="M18" t="n">
-        <v>-16.8312</v>
+        <v>-26.0181</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.2511</v>
+        <v>-15.9605</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.580299999999999</v>
+        <v>-10.0575</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.299499999999999</v>
+        <v>-8.152799999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-17.9728</v>
+        <v>-41.5042</v>
       </c>
       <c r="R18" t="n">
-        <v>11.673</v>
+        <v>33.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>5.2321</v>
+        <v>9.1592</v>
       </c>
       <c r="T18" t="n">
-        <v>6.0201</v>
+        <v>5.275799999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7884</v>
+        <v>3.8832</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0698</v>
+        <v>3.9643</v>
       </c>
       <c r="W18" t="n">
-        <v>4.0887</v>
+        <v>11.0099</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.1584</v>
+        <v>-7.045500000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PALOMO</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>-23.6113</v>
+        <v>-24.6378</v>
       </c>
       <c r="E19" t="n">
-        <v>-10.2756</v>
+        <v>-14.5573</v>
       </c>
       <c r="F19" t="n">
-        <v>-13.3358</v>
+        <v>-10.0806</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.6047</v>
+        <v>-20.6761</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5128</v>
+        <v>-16.4596</v>
       </c>
       <c r="I19" t="n">
-        <v>-8.117599999999999</v>
+        <v>-4.2166</v>
       </c>
       <c r="J19" t="n">
-        <v>8.3569</v>
+        <v>-3.8446</v>
       </c>
       <c r="K19" t="n">
-        <v>7.4827</v>
+        <v>-6.208499999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8739999999999994</v>
+        <v>2.3639</v>
       </c>
       <c r="M19" t="n">
-        <v>-13.9615</v>
+        <v>-16.8312</v>
       </c>
       <c r="N19" t="n">
-        <v>-4.970000000000001</v>
+        <v>-10.2511</v>
       </c>
       <c r="O19" t="n">
-        <v>-8.9916</v>
+        <v>-6.580299999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-5.9292</v>
+        <v>-6.299499999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-21.4933</v>
+        <v>-17.9728</v>
       </c>
       <c r="R19" t="n">
-        <v>15.564</v>
+        <v>11.673</v>
       </c>
       <c r="S19" t="n">
-        <v>-6.9165</v>
+        <v>3.4074</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.6905</v>
+        <v>3.1714</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.2258</v>
+        <v>0.2361</v>
       </c>
       <c r="V19" t="n">
-        <v>-5.1608</v>
+        <v>-1.0698</v>
       </c>
       <c r="W19" t="n">
-        <v>7.5515</v>
+        <v>4.0887</v>
       </c>
       <c r="X19" t="n">
-        <v>-12.7123</v>
+        <v>-5.1584</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-40.8556</v>
+        <v>-37.718</v>
       </c>
       <c r="E20" t="n">
-        <v>-32.7496</v>
+        <v>-29.524</v>
       </c>
       <c r="F20" t="n">
-        <v>-8.106</v>
+        <v>-8.1937</v>
       </c>
       <c r="G20" t="n">
         <v>-30.253</v>
@@ -2014,13 +2014,13 @@
         <v>32.0543</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9251999999999998</v>
+        <v>2.2122</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.8239</v>
+        <v>1.4019</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8984000000000001</v>
+        <v>0.8101</v>
       </c>
       <c r="V20" t="n">
         <v>-5.4156</v>
@@ -2047,22 +2047,22 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-163.7514</v>
+        <v>-145.857</v>
       </c>
       <c r="E21" t="n">
-        <v>-85.1514</v>
+        <v>-76.39660000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-78.59950000000001</v>
+        <v>-69.45920000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-149.0043</v>
       </c>
       <c r="H21" t="n">
-        <v>-72.43740000000001</v>
+        <v>-72.4374</v>
       </c>
       <c r="I21" t="n">
-        <v>-76.56599999999999</v>
+        <v>-76.566</v>
       </c>
       <c r="J21" t="n">
         <v>176.8855</v>
@@ -2071,7 +2071,7 @@
         <v>112.0617</v>
       </c>
       <c r="L21" t="n">
-        <v>64.8245</v>
+        <v>64.82449999999999</v>
       </c>
       <c r="M21" t="n">
         <v>-325.8893</v>
@@ -2092,16 +2092,16 @@
         <v>405.7774</v>
       </c>
       <c r="S21" t="n">
-        <v>20.7864</v>
+        <v>38.6798</v>
       </c>
       <c r="T21" t="n">
-        <v>22.9169</v>
+        <v>31.6705</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.131</v>
+        <v>7.009100000000002</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.254300000000004</v>
+        <v>-1.2543</v>
       </c>
       <c r="W21" t="n">
         <v>155.1039</v>
